--- a/reports/Debug-snowbowl-20260105/For The Week Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260105/For The Week Ending (Actual)_Revenue.xlsx
@@ -58,10 +58,10 @@
     <t xml:space="preserve">                         </t>
   </si>
   <si>
+    <t xml:space="preserve">T100                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T103                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T100                     </t>
   </si>
   <si>
     <t>department</t>
@@ -510,7 +510,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="2">
-        <v>11302.8200</v>
+        <v>123833.8000</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -524,7 +524,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="2">
-        <v>123833.8000</v>
+        <v>11302.8200</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -608,7 +608,7 @@
         <v>24</v>
       </c>
       <c r="D11" s="2">
-        <v>21774.1500</v>
+        <v>21795.7000</v>
       </c>
     </row>
     <row r="12" spans="1:4">
